--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C016BB3-6520-4F8B-A0D7-2E14D98B9D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083CD1BA-20D3-4523-9F84-A9C2577EC5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="2358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="2360">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7113,6 +7113,12 @@
   </si>
   <si>
     <t>MAURO ALEXANDER PARRA CONTRERAS</t>
+  </si>
+  <si>
+    <t>DIEGO BERNINI LOPES</t>
+  </si>
+  <si>
+    <t>LEONARDO ALVES DOS SANTOS</t>
   </si>
 </sst>
 </file>
@@ -7464,7 +7470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:B2392"/>
+  <dimension ref="A1:B2394"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
@@ -26606,6 +26612,22 @@
         <v>1444317</v>
       </c>
     </row>
+    <row r="2393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2393" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B2393">
+        <v>1444406</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2394" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B2394">
+        <v>1444456</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083CD1BA-20D3-4523-9F84-A9C2577EC5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51508492-0DD3-4144-9D9F-90985C97DFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51508492-0DD3-4144-9D9F-90985C97DFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65348A04-DA7E-44A4-AEA1-F3CE59F29314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="2371">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7119,6 +7119,39 @@
   </si>
   <si>
     <t>LEONARDO ALVES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JONATHAN HERCILIO PERIN</t>
+  </si>
+  <si>
+    <t>ADRIEL MARTINS DA SILVA</t>
+  </si>
+  <si>
+    <t>ALEX SIMOES RIBEIRO</t>
+  </si>
+  <si>
+    <t>BRUNO APARECIDO DOS SANTOS RODRIGUES</t>
+  </si>
+  <si>
+    <t>CARLOS EDUARDO PEREIRA</t>
+  </si>
+  <si>
+    <t>EDUARDO SANTANA SOBRAL</t>
+  </si>
+  <si>
+    <t>FLAVIO CAETANO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>LEONARDO ROGERIO RIBEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>LUCAS GABRIEL PONTES DA SILVA</t>
+  </si>
+  <si>
+    <t>ROBERTO NATAL PASSAGEM DE MELO</t>
+  </si>
+  <si>
+    <t>WEINY KAUAN RAMOS MORENO</t>
   </si>
 </sst>
 </file>
@@ -7470,7 +7503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:B2394"/>
+  <dimension ref="A1:B2405"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
@@ -26628,6 +26661,94 @@
         <v>1444456</v>
       </c>
     </row>
+    <row r="2395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2395" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B2395">
+        <v>1444889</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2396" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B2396">
+        <v>1128541</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2397" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B2397">
+        <v>1444883</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2398" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B2398">
+        <v>1444896</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2399" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B2399">
+        <v>1444886</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2400" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B2400">
+        <v>1444864</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2401" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B2401">
+        <v>1444888</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2402" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B2402">
+        <v>1444871</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2403" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B2403">
+        <v>1444866</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2404" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B2404">
+        <v>1444891</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2405" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B2405">
+        <v>1444882</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65348A04-DA7E-44A4-AEA1-F3CE59F29314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F364E412-9C6A-43CD-B003-79280720C94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -7187,8 +7187,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7503,7 +7504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:B2405"/>
+  <dimension ref="A1:O2405"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
@@ -26581,7 +26582,7 @@
         <v>1443939</v>
       </c>
     </row>
-    <row r="2385" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2385" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2385" t="s">
         <v>2349</v>
       </c>
@@ -26589,7 +26590,7 @@
         <v>1443918</v>
       </c>
     </row>
-    <row r="2386" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2386" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2386" t="s">
         <v>2350</v>
       </c>
@@ -26597,7 +26598,7 @@
         <v>1443911</v>
       </c>
     </row>
-    <row r="2387" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2387" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2387" t="s">
         <v>2352</v>
       </c>
@@ -26605,7 +26606,7 @@
         <v>1444176</v>
       </c>
     </row>
-    <row r="2388" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2388" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2388" t="s">
         <v>2353</v>
       </c>
@@ -26613,7 +26614,7 @@
         <v>1444164</v>
       </c>
     </row>
-    <row r="2389" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2389" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2389" t="s">
         <v>2354</v>
       </c>
@@ -26621,7 +26622,7 @@
         <v>1444249</v>
       </c>
     </row>
-    <row r="2390" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2390" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2390" t="s">
         <v>2355</v>
       </c>
@@ -26629,7 +26630,7 @@
         <v>1414454</v>
       </c>
     </row>
-    <row r="2391" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2391" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2391" t="s">
         <v>2356</v>
       </c>
@@ -26637,7 +26638,7 @@
         <v>1444305</v>
       </c>
     </row>
-    <row r="2392" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2392" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2392" t="s">
         <v>2357</v>
       </c>
@@ -26645,95 +26646,106 @@
         <v>1444317</v>
       </c>
     </row>
-    <row r="2393" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2393" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2393" t="s">
         <v>2358</v>
       </c>
       <c r="B2393">
         <v>1444406</v>
       </c>
-    </row>
-    <row r="2394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2393" s="1"/>
+    </row>
+    <row r="2394" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2394" t="s">
         <v>2359</v>
       </c>
       <c r="B2394">
         <v>1444456</v>
       </c>
-    </row>
-    <row r="2395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2394" s="1"/>
+    </row>
+    <row r="2395" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2395" t="s">
         <v>2360</v>
       </c>
       <c r="B2395">
         <v>1444889</v>
       </c>
-    </row>
-    <row r="2396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2395" s="1"/>
+    </row>
+    <row r="2396" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2396" t="s">
         <v>2361</v>
       </c>
       <c r="B2396">
         <v>1128541</v>
       </c>
-    </row>
-    <row r="2397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2396" s="1"/>
+    </row>
+    <row r="2397" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2397" t="s">
         <v>2362</v>
       </c>
       <c r="B2397">
         <v>1444883</v>
       </c>
-    </row>
-    <row r="2398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2397" s="1"/>
+    </row>
+    <row r="2398" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2398" t="s">
         <v>2363</v>
       </c>
       <c r="B2398">
         <v>1444896</v>
       </c>
-    </row>
-    <row r="2399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2398" s="1"/>
+    </row>
+    <row r="2399" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2399" t="s">
         <v>2364</v>
       </c>
       <c r="B2399">
         <v>1444886</v>
       </c>
-    </row>
-    <row r="2400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2399" s="1"/>
+    </row>
+    <row r="2400" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2400" t="s">
         <v>2365</v>
       </c>
       <c r="B2400">
         <v>1444864</v>
       </c>
-    </row>
-    <row r="2401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2400" s="1"/>
+    </row>
+    <row r="2401" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2401" t="s">
         <v>2366</v>
       </c>
       <c r="B2401">
         <v>1444888</v>
       </c>
-    </row>
-    <row r="2402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2401" s="1"/>
+    </row>
+    <row r="2402" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2402" t="s">
         <v>2367</v>
       </c>
       <c r="B2402">
         <v>1444871</v>
       </c>
-    </row>
-    <row r="2403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2402" s="1"/>
+    </row>
+    <row r="2403" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2403" t="s">
         <v>2368</v>
       </c>
       <c r="B2403">
         <v>1444866</v>
       </c>
-    </row>
-    <row r="2404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="O2403" s="1"/>
+    </row>
+    <row r="2404" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2404" t="s">
         <v>2369</v>
       </c>
@@ -26741,7 +26753,7 @@
         <v>1444891</v>
       </c>
     </row>
-    <row r="2405" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2405" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2405" t="s">
         <v>2370</v>
       </c>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F364E412-9C6A-43CD-B003-79280720C94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F921C1EF-F769-4449-9F90-0E1328AB54BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="2371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="2373">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7152,6 +7152,12 @@
   </si>
   <si>
     <t>WEINY KAUAN RAMOS MORENO</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO DA SILVA</t>
+  </si>
+  <si>
+    <t>PATRICK GAMBOA VIEIRA MACHARUTTO</t>
   </si>
 </sst>
 </file>
@@ -7504,7 +7510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2405"/>
+  <dimension ref="A1:O2407"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
@@ -26761,6 +26767,22 @@
         <v>1444882</v>
       </c>
     </row>
+    <row r="2406" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2406" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B2406">
+        <v>1445030</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2407" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B2407">
+        <v>1026790</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F921C1EF-F769-4449-9F90-0E1328AB54BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6828C9-F9D6-484F-8B36-B2A8196368F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="2373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="2374">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7158,6 +7158,9 @@
   </si>
   <si>
     <t>PATRICK GAMBOA VIEIRA MACHARUTTO</t>
+  </si>
+  <si>
+    <t>LUAN PHELIPE DE ALMEIDA ALVES</t>
   </si>
 </sst>
 </file>
@@ -7510,7 +7513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2407"/>
+  <dimension ref="A1:O2408"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
@@ -26783,6 +26786,14 @@
         <v>1026790</v>
       </c>
     </row>
+    <row r="2408" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2408" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B2408">
+        <v>1445114</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6828C9-F9D6-484F-8B36-B2A8196368F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B277BC6D-7F40-4394-A998-B53D50772EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="2374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="2379">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7161,6 +7161,21 @@
   </si>
   <si>
     <t>LUAN PHELIPE DE ALMEIDA ALVES</t>
+  </si>
+  <si>
+    <t>LEONARDO DA ROSA SCZEPANIAK</t>
+  </si>
+  <si>
+    <t>DIEGO PEDRO DA SILVA</t>
+  </si>
+  <si>
+    <t>EDENILDO BATISTA DA SILVA</t>
+  </si>
+  <si>
+    <t>GUILHERME ALVES RAMOS</t>
+  </si>
+  <si>
+    <t>MAYKE DE SOUSA LEITAO</t>
   </si>
 </sst>
 </file>
@@ -7513,7 +7528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2408"/>
+  <dimension ref="A1:O2413"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
@@ -26794,6 +26809,46 @@
         <v>1445114</v>
       </c>
     </row>
+    <row r="2409" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2409" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B2409">
+        <v>1445245</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2410" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B2410">
+        <v>1445306</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2411" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B2411">
+        <v>1445301</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2412" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B2412">
+        <v>1445307</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2413" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B2413">
+        <v>1445300</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B277BC6D-7F40-4394-A998-B53D50772EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E663CE7-99A2-4DAF-B14A-7DE11AC438EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E663CE7-99A2-4DAF-B14A-7DE11AC438EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927B7B13-E3C3-45D6-A617-47D075E4CE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C01EFE-5A73-43BD-A595-D67D55813BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DE8612-0D68-49B7-BAFD-C4899386535E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="2380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="2382">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7179,6 +7179,12 @@
   </si>
   <si>
     <t>LUIZ MARCELO CARDOSO DA SILVA</t>
+  </si>
+  <si>
+    <t>MARCOS JOSE FERREIRA</t>
+  </si>
+  <si>
+    <t>RENATO PATRICK DO NASCIMENTO</t>
   </si>
 </sst>
 </file>
@@ -7531,7 +7537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2414"/>
+  <dimension ref="A1:O2416"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -26860,6 +26866,22 @@
         <v>1446112</v>
       </c>
     </row>
+    <row r="2415" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2415" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B2415">
+        <v>1446204</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2416" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B2416">
+        <v>1446215</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DE8612-0D68-49B7-BAFD-C4899386535E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597441A1-3806-4F65-9AF7-FD9BCF4E9488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="2382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="2383">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7185,6 +7185,9 @@
   </si>
   <si>
     <t>RENATO PATRICK DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>LEONARDO DO CARMO</t>
   </si>
 </sst>
 </file>
@@ -7537,7 +7540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2416"/>
+  <dimension ref="A1:O2417"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -26882,6 +26885,14 @@
         <v>1446215</v>
       </c>
     </row>
+    <row r="2417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2417" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B2417">
+        <v>1446244</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597441A1-3806-4F65-9AF7-FD9BCF4E9488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE700942-6811-453D-BC08-A6709580E9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="2383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="2397">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7188,6 +7188,48 @@
   </si>
   <si>
     <t>LEONARDO DO CARMO</t>
+  </si>
+  <si>
+    <t>FABIO JOSE RIBEIRO GOEBEL</t>
+  </si>
+  <si>
+    <t>ROMULO BERNARDES DA SILVA ALMEIDA</t>
+  </si>
+  <si>
+    <t>EDSON CARLOS EUZEBIO DA SILVA</t>
+  </si>
+  <si>
+    <t>JOAO HENRIQUE LOBO DE ASSIS</t>
+  </si>
+  <si>
+    <t>VALDEIR JESUS DE SOUZA SANTOS</t>
+  </si>
+  <si>
+    <t>DARLAN SOUZA SANTOS</t>
+  </si>
+  <si>
+    <t>FELLIPE MARAVELLI BRITO</t>
+  </si>
+  <si>
+    <t>FRANCISCO EVANILDO PEREIRA VIEIRA</t>
+  </si>
+  <si>
+    <t>GUILHERME MENEZ DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>JOAO BATISTA DE FREITAS</t>
+  </si>
+  <si>
+    <t>KAIO ALVES BARBOSA</t>
+  </si>
+  <si>
+    <t>SIVANILSON SILVA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JEFERSON BALBINO DA SILVA</t>
+  </si>
+  <si>
+    <t>LEANDRO DE SOUZA MONTEIRO</t>
   </si>
 </sst>
 </file>
@@ -7540,10 +7582,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2417"/>
+  <dimension ref="A1:O2431"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -26891,6 +26934,118 @@
       </c>
       <c r="B2417">
         <v>1446244</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2418" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B2418">
+        <v>1446457</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2419" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B2419">
+        <v>1446481</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2420" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B2420">
+        <v>1446474</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2421" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B2421">
+        <v>1446489</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2422" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B2422">
+        <v>1446486</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2423" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B2423">
+        <v>1446497</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2424" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B2424">
+        <v>1446490</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2425" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B2425">
+        <v>1149525</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2426" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B2426">
+        <v>1446472</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2427" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B2427">
+        <v>1395129</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2428" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B2428">
+        <v>1446482</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2429" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B2429">
+        <v>1446473</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2430" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B2430">
+        <v>1446479</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2431" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B2431">
+        <v>1446496</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE700942-6811-453D-BC08-A6709580E9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7C6FA4-2270-4EA8-898B-C7304B716213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="2397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="2401">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7230,13 +7230,25 @@
   </si>
   <si>
     <t>LEANDRO DE SOUZA MONTEIRO</t>
+  </si>
+  <si>
+    <t>ALLAN THALES DOS SANTOS LEAL</t>
+  </si>
+  <si>
+    <t>ELIEZER LOUBET ACHUCARRO</t>
+  </si>
+  <si>
+    <t>SAULO MAIKE CASTILHO</t>
+  </si>
+  <si>
+    <t>VITOR HUGO DE CARVALHO PARMANHANI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7244,16 +7256,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -7261,13 +7283,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA9A9A9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA9A9A9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9A9A9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7582,7 +7622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2431"/>
+  <dimension ref="A1:O2447"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -26928,7 +26968,7 @@
         <v>1446215</v>
       </c>
     </row>
-    <row r="2417" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2417" t="s">
         <v>2382</v>
       </c>
@@ -26936,7 +26976,7 @@
         <v>1446244</v>
       </c>
     </row>
-    <row r="2418" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2418" t="s">
         <v>2383</v>
       </c>
@@ -26944,7 +26984,7 @@
         <v>1446457</v>
       </c>
     </row>
-    <row r="2419" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2419" t="s">
         <v>2384</v>
       </c>
@@ -26952,7 +26992,7 @@
         <v>1446481</v>
       </c>
     </row>
-    <row r="2420" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2420" t="s">
         <v>2385</v>
       </c>
@@ -26960,7 +27000,7 @@
         <v>1446474</v>
       </c>
     </row>
-    <row r="2421" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2421" t="s">
         <v>2386</v>
       </c>
@@ -26968,85 +27008,167 @@
         <v>1446489</v>
       </c>
     </row>
-    <row r="2422" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2422" t="s">
         <v>2387</v>
       </c>
       <c r="B2422">
         <v>1446486</v>
       </c>
-    </row>
-    <row r="2423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F2422" s="2"/>
+    </row>
+    <row r="2423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2423" t="s">
         <v>2388</v>
       </c>
       <c r="B2423">
         <v>1446497</v>
       </c>
-    </row>
-    <row r="2424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F2423" s="2"/>
+    </row>
+    <row r="2424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2424" t="s">
         <v>2389</v>
       </c>
       <c r="B2424">
         <v>1446490</v>
       </c>
-    </row>
-    <row r="2425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F2424" s="2"/>
+    </row>
+    <row r="2425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2425" t="s">
         <v>2390</v>
       </c>
       <c r="B2425">
         <v>1149525</v>
       </c>
-    </row>
-    <row r="2426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F2425" s="2"/>
+    </row>
+    <row r="2426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2426" t="s">
         <v>2391</v>
       </c>
       <c r="B2426">
         <v>1446472</v>
       </c>
-    </row>
-    <row r="2427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F2426" s="2"/>
+    </row>
+    <row r="2427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2427" t="s">
         <v>2392</v>
       </c>
       <c r="B2427">
         <v>1395129</v>
       </c>
-    </row>
-    <row r="2428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F2427" s="2"/>
+    </row>
+    <row r="2428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2428" t="s">
         <v>2393</v>
       </c>
       <c r="B2428">
         <v>1446482</v>
       </c>
-    </row>
-    <row r="2429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F2428" s="2"/>
+    </row>
+    <row r="2429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2429" t="s">
         <v>2394</v>
       </c>
       <c r="B2429">
         <v>1446473</v>
       </c>
-    </row>
-    <row r="2430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F2429" s="2"/>
+    </row>
+    <row r="2430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2430" t="s">
         <v>2395</v>
       </c>
       <c r="B2430">
         <v>1446479</v>
       </c>
-    </row>
-    <row r="2431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F2430" s="2"/>
+    </row>
+    <row r="2431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2431" t="s">
         <v>2396</v>
       </c>
       <c r="B2431">
         <v>1446496</v>
       </c>
+      <c r="F2431" s="2"/>
+    </row>
+    <row r="2432" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2432" s="2" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B2432">
+        <v>1007318</v>
+      </c>
+      <c r="F2432" s="2"/>
+    </row>
+    <row r="2433" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2433" s="2" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B2433">
+        <v>1446526</v>
+      </c>
+      <c r="F2433" s="2"/>
+    </row>
+    <row r="2434" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2434" s="2" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B2434">
+        <v>1446515</v>
+      </c>
+      <c r="F2434" s="2"/>
+    </row>
+    <row r="2435" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2435" s="2" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B2435">
+        <v>1446521</v>
+      </c>
+      <c r="F2435" s="2"/>
+    </row>
+    <row r="2436" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2436" s="2"/>
+    </row>
+    <row r="2437" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2437" s="2"/>
+    </row>
+    <row r="2438" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2438" s="2"/>
+    </row>
+    <row r="2439" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2439" s="2"/>
+    </row>
+    <row r="2440" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2440" s="2"/>
+    </row>
+    <row r="2441" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2441" s="2"/>
+    </row>
+    <row r="2442" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2442" s="2"/>
+    </row>
+    <row r="2443" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2443" s="2"/>
+    </row>
+    <row r="2444" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2444" s="2"/>
+    </row>
+    <row r="2445" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2445" s="2"/>
+    </row>
+    <row r="2446" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2446" s="2"/>
+    </row>
+    <row r="2447" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2447" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7C6FA4-2270-4EA8-898B-C7304B716213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D85FB00-2B75-4B54-97EA-6E4E99F7E98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="2401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="2408">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7242,6 +7242,27 @@
   </si>
   <si>
     <t>VITOR HUGO DE CARVALHO PARMANHANI</t>
+  </si>
+  <si>
+    <t>ROBSON DE SOUZA GOMES</t>
+  </si>
+  <si>
+    <t>WALLACE CARDOZO CUNHA</t>
+  </si>
+  <si>
+    <t>ANDERSON EDMILSON DA SILVA</t>
+  </si>
+  <si>
+    <t>EMERSON SANTANA MACHADO</t>
+  </si>
+  <si>
+    <t>JOAQUIM FERNANDES DE OLIVEIRA JUNIOR</t>
+  </si>
+  <si>
+    <t>JOHN HEBERT MARCOS GOMES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>LUAN DE LIMA ANDRADE</t>
   </si>
 </sst>
 </file>
@@ -7622,7 +7643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2447"/>
+  <dimension ref="A1:O2449"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27135,24 +27156,66 @@
       <c r="F2435" s="2"/>
     </row>
     <row r="2436" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2436" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B2436">
+        <v>1446606</v>
+      </c>
       <c r="F2436" s="2"/>
     </row>
     <row r="2437" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2437" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B2437">
+        <v>1446621</v>
+      </c>
       <c r="F2437" s="2"/>
     </row>
     <row r="2438" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2438" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B2438">
+        <v>1446718</v>
+      </c>
       <c r="F2438" s="2"/>
     </row>
     <row r="2439" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2439" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B2439">
+        <v>1446710</v>
+      </c>
       <c r="F2439" s="2"/>
     </row>
     <row r="2440" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2440" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B2440">
+        <v>1446699</v>
+      </c>
       <c r="F2440" s="2"/>
     </row>
     <row r="2441" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2441" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B2441">
+        <v>1446700</v>
+      </c>
       <c r="F2441" s="2"/>
     </row>
     <row r="2442" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2442" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B2442">
+        <v>1446661</v>
+      </c>
       <c r="F2442" s="2"/>
     </row>
     <row r="2443" spans="1:6" x14ac:dyDescent="0.3">
@@ -27169,6 +27232,12 @@
     </row>
     <row r="2447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F2447" s="2"/>
+    </row>
+    <row r="2448" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2448" s="2"/>
+    </row>
+    <row r="2449" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F2449" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D85FB00-2B75-4B54-97EA-6E4E99F7E98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F744359F-2C54-4900-9468-26880693886A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="2408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="2424">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7263,6 +7263,54 @@
   </si>
   <si>
     <t>LUAN DE LIMA ANDRADE</t>
+  </si>
+  <si>
+    <t>EVANILSON DOS ANJOS SIQUEIRA</t>
+  </si>
+  <si>
+    <t>RAFAEL SILVA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO DE SOUZA SANTOS</t>
+  </si>
+  <si>
+    <t>WILLAMS FERREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>ALLAN BERNARDO DA COSTA</t>
+  </si>
+  <si>
+    <t>CAIO AMORIM DOS SANTOS</t>
+  </si>
+  <si>
+    <t>CAIO VIANA MELO</t>
+  </si>
+  <si>
+    <t>FAGNER GALDINO DE SOUSA</t>
+  </si>
+  <si>
+    <t>GUILHERME SANTOS DA SILVA</t>
+  </si>
+  <si>
+    <t>JONAS SIQUEIRA SANCHO</t>
+  </si>
+  <si>
+    <t>JONATHAN RAMOS VIEIRA</t>
+  </si>
+  <si>
+    <t>ADRIAN SILVA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>CAIO CESAR DA SILVA AMARO</t>
+  </si>
+  <si>
+    <t>WESLLEY KAUA MOURA FERREIRA</t>
+  </si>
+  <si>
+    <t>ANDERSON PEREIRA DE LARA</t>
+  </si>
+  <si>
+    <t>FABIO JUNIOR SANTANA DUTRA</t>
   </si>
 </sst>
 </file>
@@ -7323,12 +7371,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7643,7 +7692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2449"/>
+  <dimension ref="A1:O2458"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27219,25 +27268,139 @@
       <c r="F2442" s="2"/>
     </row>
     <row r="2443" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2443" s="2" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B2443" s="3">
+        <v>1446814</v>
+      </c>
       <c r="F2443" s="2"/>
     </row>
     <row r="2444" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2444" s="2" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B2444" s="3">
+        <v>1446832</v>
+      </c>
       <c r="F2444" s="2"/>
     </row>
     <row r="2445" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2445" s="2" t="s">
+        <v>2410</v>
+      </c>
+      <c r="B2445" s="3">
+        <v>1446826</v>
+      </c>
       <c r="F2445" s="2"/>
     </row>
     <row r="2446" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2446" s="2" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B2446" s="3">
+        <v>1446825</v>
+      </c>
       <c r="F2446" s="2"/>
     </row>
     <row r="2447" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2447" s="2" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B2447" s="3">
+        <v>1446865</v>
+      </c>
       <c r="F2447" s="2"/>
     </row>
     <row r="2448" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2448" s="2" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B2448" s="3">
+        <v>1446856</v>
+      </c>
       <c r="F2448" s="2"/>
     </row>
-    <row r="2449" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="2449" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2449" s="2" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B2449" s="3">
+        <v>1446858</v>
+      </c>
       <c r="F2449" s="2"/>
+    </row>
+    <row r="2450" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2450" s="2" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B2450" s="3">
+        <v>1104264</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2451" s="2" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B2451" s="3">
+        <v>1446810</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2452" s="2" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B2452" s="3">
+        <v>1145287</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2453" s="2" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B2453" s="3">
+        <v>1446809</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2454" s="2" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B2454" s="3">
+        <v>1446869</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2455" s="2" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B2455" s="3">
+        <v>1446861</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2456" s="2" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B2456" s="3">
+        <v>1446823</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2457" s="2" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B2457" s="3">
+        <v>1446864</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2458" s="2" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B2458" s="3">
+        <v>1446850</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F744359F-2C54-4900-9468-26880693886A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B1DABA-4BE5-4F79-91FA-1901A2905CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -7371,13 +7371,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7692,11 +7691,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:O2458"/>
+  <dimension ref="A1:C2458"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -26771,7 +26769,7 @@
         <v>1443939</v>
       </c>
     </row>
-    <row r="2385" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2385" t="s">
         <v>2349</v>
       </c>
@@ -26779,7 +26777,7 @@
         <v>1443918</v>
       </c>
     </row>
-    <row r="2386" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2386" t="s">
         <v>2350</v>
       </c>
@@ -26787,7 +26785,7 @@
         <v>1443911</v>
       </c>
     </row>
-    <row r="2387" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2387" t="s">
         <v>2352</v>
       </c>
@@ -26795,7 +26793,7 @@
         <v>1444176</v>
       </c>
     </row>
-    <row r="2388" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2388" t="s">
         <v>2353</v>
       </c>
@@ -26803,7 +26801,7 @@
         <v>1444164</v>
       </c>
     </row>
-    <row r="2389" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2389" t="s">
         <v>2354</v>
       </c>
@@ -26811,7 +26809,7 @@
         <v>1444249</v>
       </c>
     </row>
-    <row r="2390" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2390" t="s">
         <v>2355</v>
       </c>
@@ -26819,7 +26817,7 @@
         <v>1414454</v>
       </c>
     </row>
-    <row r="2391" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2391" t="s">
         <v>2356</v>
       </c>
@@ -26827,7 +26825,7 @@
         <v>1444305</v>
       </c>
     </row>
-    <row r="2392" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2392" t="s">
         <v>2357</v>
       </c>
@@ -26835,106 +26833,106 @@
         <v>1444317</v>
       </c>
     </row>
-    <row r="2393" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2393" t="s">
         <v>2358</v>
       </c>
       <c r="B2393">
         <v>1444406</v>
       </c>
-      <c r="O2393" s="1"/>
-    </row>
-    <row r="2394" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2393" s="1"/>
+    </row>
+    <row r="2394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2394" t="s">
         <v>2359</v>
       </c>
       <c r="B2394">
         <v>1444456</v>
       </c>
-      <c r="O2394" s="1"/>
-    </row>
-    <row r="2395" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2394" s="1"/>
+    </row>
+    <row r="2395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2395" t="s">
         <v>2360</v>
       </c>
       <c r="B2395">
         <v>1444889</v>
       </c>
-      <c r="O2395" s="1"/>
-    </row>
-    <row r="2396" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2395" s="1"/>
+    </row>
+    <row r="2396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2396" t="s">
         <v>2361</v>
       </c>
       <c r="B2396">
         <v>1128541</v>
       </c>
-      <c r="O2396" s="1"/>
-    </row>
-    <row r="2397" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2396" s="1"/>
+    </row>
+    <row r="2397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2397" t="s">
         <v>2362</v>
       </c>
       <c r="B2397">
         <v>1444883</v>
       </c>
-      <c r="O2397" s="1"/>
-    </row>
-    <row r="2398" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2397" s="1"/>
+    </row>
+    <row r="2398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2398" t="s">
         <v>2363</v>
       </c>
       <c r="B2398">
         <v>1444896</v>
       </c>
-      <c r="O2398" s="1"/>
-    </row>
-    <row r="2399" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2398" s="1"/>
+    </row>
+    <row r="2399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2399" t="s">
         <v>2364</v>
       </c>
       <c r="B2399">
         <v>1444886</v>
       </c>
-      <c r="O2399" s="1"/>
-    </row>
-    <row r="2400" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2399" s="1"/>
+    </row>
+    <row r="2400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2400" t="s">
         <v>2365</v>
       </c>
       <c r="B2400">
         <v>1444864</v>
       </c>
-      <c r="O2400" s="1"/>
-    </row>
-    <row r="2401" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2400" s="1"/>
+    </row>
+    <row r="2401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2401" t="s">
         <v>2366</v>
       </c>
       <c r="B2401">
         <v>1444888</v>
       </c>
-      <c r="O2401" s="1"/>
-    </row>
-    <row r="2402" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2401" s="1"/>
+    </row>
+    <row r="2402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2402" t="s">
         <v>2367</v>
       </c>
       <c r="B2402">
         <v>1444871</v>
       </c>
-      <c r="O2402" s="1"/>
-    </row>
-    <row r="2403" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2402" s="1"/>
+    </row>
+    <row r="2403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2403" t="s">
         <v>2368</v>
       </c>
       <c r="B2403">
         <v>1444866</v>
       </c>
-      <c r="O2403" s="1"/>
-    </row>
-    <row r="2404" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2403" s="1"/>
+    </row>
+    <row r="2404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2404" t="s">
         <v>2369</v>
       </c>
@@ -26942,7 +26940,7 @@
         <v>1444891</v>
       </c>
     </row>
-    <row r="2405" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2405" t="s">
         <v>2370</v>
       </c>
@@ -26950,7 +26948,7 @@
         <v>1444882</v>
       </c>
     </row>
-    <row r="2406" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2406" t="s">
         <v>2371</v>
       </c>
@@ -26958,7 +26956,7 @@
         <v>1445030</v>
       </c>
     </row>
-    <row r="2407" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2407" t="s">
         <v>2372</v>
       </c>
@@ -26966,7 +26964,7 @@
         <v>1026790</v>
       </c>
     </row>
-    <row r="2408" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2408" t="s">
         <v>2373</v>
       </c>
@@ -26974,7 +26972,7 @@
         <v>1445114</v>
       </c>
     </row>
-    <row r="2409" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2409" t="s">
         <v>2374</v>
       </c>
@@ -26982,7 +26980,7 @@
         <v>1445245</v>
       </c>
     </row>
-    <row r="2410" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2410" t="s">
         <v>2375</v>
       </c>
@@ -26990,7 +26988,7 @@
         <v>1445306</v>
       </c>
     </row>
-    <row r="2411" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2411" t="s">
         <v>2376</v>
       </c>
@@ -26998,7 +26996,7 @@
         <v>1445301</v>
       </c>
     </row>
-    <row r="2412" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2412" t="s">
         <v>2377</v>
       </c>
@@ -27006,7 +27004,7 @@
         <v>1445307</v>
       </c>
     </row>
-    <row r="2413" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2413" t="s">
         <v>2378</v>
       </c>
@@ -27014,7 +27012,7 @@
         <v>1445300</v>
       </c>
     </row>
-    <row r="2414" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2414" t="s">
         <v>2379</v>
       </c>
@@ -27022,7 +27020,7 @@
         <v>1446112</v>
       </c>
     </row>
-    <row r="2415" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2415" t="s">
         <v>2380</v>
       </c>
@@ -27030,7 +27028,7 @@
         <v>1446204</v>
       </c>
     </row>
-    <row r="2416" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2416" t="s">
         <v>2381</v>
       </c>
@@ -27038,7 +27036,7 @@
         <v>1446215</v>
       </c>
     </row>
-    <row r="2417" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2417" t="s">
         <v>2382</v>
       </c>
@@ -27046,7 +27044,7 @@
         <v>1446244</v>
       </c>
     </row>
-    <row r="2418" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2418" t="s">
         <v>2383</v>
       </c>
@@ -27054,7 +27052,7 @@
         <v>1446457</v>
       </c>
     </row>
-    <row r="2419" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2419" t="s">
         <v>2384</v>
       </c>
@@ -27062,7 +27060,7 @@
         <v>1446481</v>
       </c>
     </row>
-    <row r="2420" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2420" t="s">
         <v>2385</v>
       </c>
@@ -27070,7 +27068,7 @@
         <v>1446474</v>
       </c>
     </row>
-    <row r="2421" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2421" t="s">
         <v>2386</v>
       </c>
@@ -27078,327 +27076,299 @@
         <v>1446489</v>
       </c>
     </row>
-    <row r="2422" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2422" t="s">
         <v>2387</v>
       </c>
       <c r="B2422">
         <v>1446486</v>
       </c>
-      <c r="F2422" s="2"/>
-    </row>
-    <row r="2423" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2423" t="s">
         <v>2388</v>
       </c>
       <c r="B2423">
         <v>1446497</v>
       </c>
-      <c r="F2423" s="2"/>
-    </row>
-    <row r="2424" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2424" t="s">
         <v>2389</v>
       </c>
       <c r="B2424">
         <v>1446490</v>
       </c>
-      <c r="F2424" s="2"/>
-    </row>
-    <row r="2425" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2425" t="s">
         <v>2390</v>
       </c>
       <c r="B2425">
         <v>1149525</v>
       </c>
-      <c r="F2425" s="2"/>
-    </row>
-    <row r="2426" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2426" t="s">
         <v>2391</v>
       </c>
       <c r="B2426">
         <v>1446472</v>
       </c>
-      <c r="F2426" s="2"/>
-    </row>
-    <row r="2427" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2427" t="s">
         <v>2392</v>
       </c>
       <c r="B2427">
         <v>1395129</v>
       </c>
-      <c r="F2427" s="2"/>
-    </row>
-    <row r="2428" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2428" t="s">
         <v>2393</v>
       </c>
       <c r="B2428">
         <v>1446482</v>
       </c>
-      <c r="F2428" s="2"/>
-    </row>
-    <row r="2429" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2429" t="s">
         <v>2394</v>
       </c>
       <c r="B2429">
         <v>1446473</v>
       </c>
-      <c r="F2429" s="2"/>
-    </row>
-    <row r="2430" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2430" t="s">
         <v>2395</v>
       </c>
       <c r="B2430">
         <v>1446479</v>
       </c>
-      <c r="F2430" s="2"/>
-    </row>
-    <row r="2431" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2431" t="s">
         <v>2396</v>
       </c>
       <c r="B2431">
         <v>1446496</v>
       </c>
-      <c r="F2431" s="2"/>
-    </row>
-    <row r="2432" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2432" s="2" t="s">
         <v>2397</v>
       </c>
       <c r="B2432">
         <v>1007318</v>
       </c>
-      <c r="F2432" s="2"/>
-    </row>
-    <row r="2433" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2433" s="2" t="s">
         <v>2398</v>
       </c>
       <c r="B2433">
         <v>1446526</v>
       </c>
-      <c r="F2433" s="2"/>
-    </row>
-    <row r="2434" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2434" s="2" t="s">
         <v>2399</v>
       </c>
       <c r="B2434">
         <v>1446515</v>
       </c>
-      <c r="F2434" s="2"/>
-    </row>
-    <row r="2435" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2435" s="2" t="s">
         <v>2400</v>
       </c>
       <c r="B2435">
         <v>1446521</v>
       </c>
-      <c r="F2435" s="2"/>
-    </row>
-    <row r="2436" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2436" t="s">
         <v>2401</v>
       </c>
       <c r="B2436">
         <v>1446606</v>
       </c>
-      <c r="F2436" s="2"/>
-    </row>
-    <row r="2437" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2437" t="s">
         <v>2402</v>
       </c>
       <c r="B2437">
         <v>1446621</v>
       </c>
-      <c r="F2437" s="2"/>
-    </row>
-    <row r="2438" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2438" t="s">
         <v>2403</v>
       </c>
       <c r="B2438">
         <v>1446718</v>
       </c>
-      <c r="F2438" s="2"/>
-    </row>
-    <row r="2439" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2439" t="s">
         <v>2404</v>
       </c>
       <c r="B2439">
         <v>1446710</v>
       </c>
-      <c r="F2439" s="2"/>
-    </row>
-    <row r="2440" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2440" t="s">
         <v>2405</v>
       </c>
       <c r="B2440">
         <v>1446699</v>
       </c>
-      <c r="F2440" s="2"/>
-    </row>
-    <row r="2441" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2441" t="s">
         <v>2406</v>
       </c>
       <c r="B2441">
         <v>1446700</v>
       </c>
-      <c r="F2441" s="2"/>
-    </row>
-    <row r="2442" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2442" t="s">
         <v>2407</v>
       </c>
       <c r="B2442">
         <v>1446661</v>
       </c>
-      <c r="F2442" s="2"/>
-    </row>
-    <row r="2443" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2443" s="2" t="s">
+    </row>
+    <row r="2443" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2443" t="s">
         <v>2408</v>
       </c>
-      <c r="B2443" s="3">
+      <c r="B2443">
         <v>1446814</v>
       </c>
-      <c r="F2443" s="2"/>
-    </row>
-    <row r="2444" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2444" s="2" t="s">
+    </row>
+    <row r="2444" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2444" t="s">
         <v>2409</v>
       </c>
-      <c r="B2444" s="3">
+      <c r="B2444">
         <v>1446832</v>
       </c>
-      <c r="F2444" s="2"/>
-    </row>
-    <row r="2445" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2445" s="2" t="s">
+    </row>
+    <row r="2445" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2445" t="s">
         <v>2410</v>
       </c>
-      <c r="B2445" s="3">
+      <c r="B2445">
         <v>1446826</v>
       </c>
-      <c r="F2445" s="2"/>
-    </row>
-    <row r="2446" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2446" s="2" t="s">
+    </row>
+    <row r="2446" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2446" t="s">
         <v>2411</v>
       </c>
-      <c r="B2446" s="3">
+      <c r="B2446">
         <v>1446825</v>
       </c>
-      <c r="F2446" s="2"/>
-    </row>
-    <row r="2447" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2447" s="2" t="s">
+    </row>
+    <row r="2447" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2447" t="s">
         <v>2412</v>
       </c>
-      <c r="B2447" s="3">
+      <c r="B2447">
         <v>1446865</v>
       </c>
-      <c r="F2447" s="2"/>
-    </row>
-    <row r="2448" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2448" s="2" t="s">
+    </row>
+    <row r="2448" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2448" t="s">
         <v>2413</v>
       </c>
-      <c r="B2448" s="3">
+      <c r="B2448">
         <v>1446856</v>
       </c>
-      <c r="F2448" s="2"/>
-    </row>
-    <row r="2449" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2449" s="2" t="s">
+    </row>
+    <row r="2449" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2449" t="s">
         <v>2414</v>
       </c>
-      <c r="B2449" s="3">
+      <c r="B2449">
         <v>1446858</v>
       </c>
-      <c r="F2449" s="2"/>
-    </row>
-    <row r="2450" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2450" s="2" t="s">
+    </row>
+    <row r="2450" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2450" t="s">
         <v>2415</v>
       </c>
-      <c r="B2450" s="3">
+      <c r="B2450">
         <v>1104264</v>
       </c>
     </row>
-    <row r="2451" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2451" s="2" t="s">
+    <row r="2451" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2451" t="s">
         <v>2416</v>
       </c>
-      <c r="B2451" s="3">
+      <c r="B2451">
         <v>1446810</v>
       </c>
     </row>
-    <row r="2452" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2452" s="2" t="s">
+    <row r="2452" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2452" t="s">
         <v>2417</v>
       </c>
-      <c r="B2452" s="3">
+      <c r="B2452">
         <v>1145287</v>
       </c>
     </row>
-    <row r="2453" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2453" s="2" t="s">
+    <row r="2453" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2453" t="s">
         <v>2418</v>
       </c>
-      <c r="B2453" s="3">
+      <c r="B2453">
         <v>1446809</v>
       </c>
     </row>
-    <row r="2454" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2454" s="2" t="s">
+    <row r="2454" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2454" t="s">
         <v>2419</v>
       </c>
-      <c r="B2454" s="3">
+      <c r="B2454">
         <v>1446869</v>
       </c>
     </row>
-    <row r="2455" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2455" s="2" t="s">
+    <row r="2455" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2455" t="s">
         <v>2420</v>
       </c>
-      <c r="B2455" s="3">
+      <c r="B2455">
         <v>1446861</v>
       </c>
     </row>
-    <row r="2456" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2456" s="2" t="s">
+    <row r="2456" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2456" t="s">
         <v>2421</v>
       </c>
-      <c r="B2456" s="3">
+      <c r="B2456">
         <v>1446823</v>
       </c>
     </row>
-    <row r="2457" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2457" s="2" t="s">
+    <row r="2457" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2457" t="s">
         <v>2422</v>
       </c>
-      <c r="B2457" s="3">
+      <c r="B2457">
         <v>1446864</v>
       </c>
     </row>
-    <row r="2458" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2458" s="2" t="s">
+    <row r="2458" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2458" t="s">
         <v>2423</v>
       </c>
-      <c r="B2458" s="3">
+      <c r="B2458">
         <v>1446850</v>
       </c>
     </row>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B1DABA-4BE5-4F79-91FA-1901A2905CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46505B8-A8A8-4FE2-872C-C8E9F3D33E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="2424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2467" uniqueCount="2428">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7311,6 +7311,18 @@
   </si>
   <si>
     <t>FABIO JUNIOR SANTANA DUTRA</t>
+  </si>
+  <si>
+    <t>RENATO DA SILVA RIBEIRO</t>
+  </si>
+  <si>
+    <t>RICARDO CAPOSSE</t>
+  </si>
+  <si>
+    <t>DIEGO DE SOUZA PAIVA</t>
+  </si>
+  <si>
+    <t>JONAS DAS NEVES VENTURA</t>
   </si>
 </sst>
 </file>
@@ -7329,6 +7341,7 @@
       <sz val="9.75"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -7691,7 +7704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2458"/>
+  <dimension ref="A1:C2466"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27372,6 +27385,70 @@
         <v>1446850</v>
       </c>
     </row>
+    <row r="2459" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2459" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B2459">
+        <v>1446904</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2460" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B2460">
+        <v>854903</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2461" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B2461">
+        <v>1446927</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2462" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B2462">
+        <v>1446932</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2463" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B2463">
+        <v>1446814</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2464" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B2464">
+        <v>1446832</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2465" t="s">
+        <v>2410</v>
+      </c>
+      <c r="B2465">
+        <v>1446826</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2466" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B2466">
+        <v>1446825</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46505B8-A8A8-4FE2-872C-C8E9F3D33E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89953E5-F1A0-4C88-8FB9-C0A0426666BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2467" uniqueCount="2428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="2431">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7323,6 +7323,15 @@
   </si>
   <si>
     <t>JONAS DAS NEVES VENTURA</t>
+  </si>
+  <si>
+    <t>HALBERT DOS SANTOS LEITE</t>
+  </si>
+  <si>
+    <t>RAFAEL DE ALMEIDA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>RONALD EDUARDO SOSA SALAZAR</t>
   </si>
 </sst>
 </file>
@@ -7704,7 +7713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2466"/>
+  <dimension ref="A1:C2469"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27449,6 +27458,27 @@
         <v>1446825</v>
       </c>
     </row>
+    <row r="2467" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2467" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2468" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B2468">
+        <v>1447090</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2469" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B2469">
+        <v>1447091</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89953E5-F1A0-4C88-8FB9-C0A0426666BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB02A4AC-9DF9-4D52-8F94-08C726381037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="2431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="2434">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7332,6 +7332,15 @@
   </si>
   <si>
     <t>RONALD EDUARDO SOSA SALAZAR</t>
+  </si>
+  <si>
+    <t>ANTONIO CARLOS DOS SANTOS COURTY SIQUEIRA</t>
+  </si>
+  <si>
+    <t>JOAO PICOLLI NOVAES</t>
+  </si>
+  <si>
+    <t>LEANDRO GALDINO DE OLIVEIRA SANTOS</t>
   </si>
 </sst>
 </file>
@@ -7713,7 +7722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2469"/>
+  <dimension ref="A1:C2472"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27462,6 +27471,9 @@
       <c r="A2467" t="s">
         <v>2428</v>
       </c>
+      <c r="B2467">
+        <v>1447158</v>
+      </c>
     </row>
     <row r="2468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2468" t="s">
@@ -27477,6 +27489,30 @@
       </c>
       <c r="B2469">
         <v>1447091</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2470" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B2470">
+        <v>1447171</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2471" t="s">
+        <v>2432</v>
+      </c>
+      <c r="B2471">
+        <v>1447126</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2472" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B2472">
+        <v>1447153</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB02A4AC-9DF9-4D52-8F94-08C726381037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB55CC36-26F7-487D-8D3B-DF4C1172ED63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB55CC36-26F7-487D-8D3B-DF4C1172ED63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE68B1B-184F-4871-A584-071754CF0466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="2434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="2451">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7341,6 +7341,57 @@
   </si>
   <si>
     <t>LEANDRO GALDINO DE OLIVEIRA SANTOS</t>
+  </si>
+  <si>
+    <t>AIRTON FRANCISCO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>DOUGLAS ROCHA DE SOUSA</t>
+  </si>
+  <si>
+    <t>ENDREWS LUAN ISIDORO DA SILVA</t>
+  </si>
+  <si>
+    <t>GIOVANNI WESLEY RIBEIRO CARVALHO</t>
+  </si>
+  <si>
+    <t>JORGE DIAS BARBOSA</t>
+  </si>
+  <si>
+    <t>MARCIO DOS SANTOS LIMA FILHO</t>
+  </si>
+  <si>
+    <t>PEDRO HENRIQUE COUTO MOREIRA</t>
+  </si>
+  <si>
+    <t>ROBINSON DA SILVA COSTA</t>
+  </si>
+  <si>
+    <t>LUCAS FALCK DOS ANJOS SIQUEIRA</t>
+  </si>
+  <si>
+    <t>FERNANDO JOSUE ANDARA ALBORNOZ</t>
+  </si>
+  <si>
+    <t>JOSE RONALDSON SOUSA DA COSTA</t>
+  </si>
+  <si>
+    <t>ARTHUR NOGUEIRA DA CONCEICAO</t>
+  </si>
+  <si>
+    <t>ALEXANDRE EDUARDO DA SILVA</t>
+  </si>
+  <si>
+    <t>ECTOR LUDIERY REIS</t>
+  </si>
+  <si>
+    <t>GABRIEL RIBEIRO LUONGO</t>
+  </si>
+  <si>
+    <t>VAGUINER JOSE DOS SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	1447527</t>
   </si>
 </sst>
 </file>
@@ -7722,7 +7773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2472"/>
+  <dimension ref="A1:C2488"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27515,6 +27566,134 @@
         <v>1447153</v>
       </c>
     </row>
+    <row r="2473" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2473" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B2473">
+        <v>1447374</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2474" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B2474">
+        <v>1447362</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2475" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B2475">
+        <v>1447359</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2476" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B2476">
+        <v>1447357</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2477" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B2477">
+        <v>1447355</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2478" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B2478">
+        <v>1447348</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2479" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B2479">
+        <v>1447305</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2480" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B2480">
+        <v>1447337</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2481" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B2481">
+        <v>1447421</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2482" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B2482">
+        <v>1447431</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2483" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B2483">
+        <v>1447424</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2484" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B2484">
+        <v>1410185</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2485" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B2485">
+        <v>1447565</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2486" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B2486">
+        <v>1447558</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2487" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B2487">
+        <v>1447553</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2488" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B2488" t="s">
+        <v>2450</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE68B1B-184F-4871-A584-071754CF0466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2898A1E6-4A2F-44F0-9D40-B5E1C7F33467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="2451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="2461">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7392,6 +7392,36 @@
   </si>
   <si>
     <t xml:space="preserve">	1447527</t>
+  </si>
+  <si>
+    <t>ADRYANO LOPES BORGES</t>
+  </si>
+  <si>
+    <t>ALLAN GONCALVES LONGO</t>
+  </si>
+  <si>
+    <t>FELIPE UCHOA SILVA</t>
+  </si>
+  <si>
+    <t>KAIKY DA SILVA BATISTA</t>
+  </si>
+  <si>
+    <t>LEONARDO SILVA SOUSA DE JESUS</t>
+  </si>
+  <si>
+    <t>RAFAEL PEREIRA PEDRO</t>
+  </si>
+  <si>
+    <t>TIAGO SEVERIANO</t>
+  </si>
+  <si>
+    <t>CARLOS NATHAN DO CARMO PEREIRA</t>
+  </si>
+  <si>
+    <t>DIOGO LEONARDO SILVA DE MELLO</t>
+  </si>
+  <si>
+    <t>GLEISON SILVA MARTINS</t>
   </si>
 </sst>
 </file>
@@ -7773,7 +7803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2488"/>
+  <dimension ref="A1:C2498"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27694,6 +27724,86 @@
         <v>2450</v>
       </c>
     </row>
+    <row r="2489" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2489" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B2489">
+        <v>1447608</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2490" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B2490">
+        <v>1447617</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2491" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B2491">
+        <v>1447598</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2492" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B2492">
+        <v>1447609</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2493" t="s">
+        <v>2455</v>
+      </c>
+      <c r="B2493">
+        <v>1447596</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2494" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B2494">
+        <v>1447606</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2495" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B2495">
+        <v>1113248</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2496" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B2496">
+        <v>1447630</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2497" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B2497">
+        <v>854218</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2498" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B2498">
+        <v>1447599</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2898A1E6-4A2F-44F0-9D40-B5E1C7F33467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8892D1A9-3A44-4AB0-B79E-38D674BA2D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IDs Logon'!$A$1:$B$2386</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IDs Logon'!$A$1:$B$2509</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="2461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="2472">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7422,6 +7422,39 @@
   </si>
   <si>
     <t>GLEISON SILVA MARTINS</t>
+  </si>
+  <si>
+    <t>BRENDO IBER SINTZ</t>
+  </si>
+  <si>
+    <t>MARCELO APARECIDO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>VALMIR CORREIA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JURANDIR DA SILVA DIAS JUNIOR</t>
+  </si>
+  <si>
+    <t>NICOLAS RIBEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>RAPHAEL ALEXANDRE DE OLIVEIRA GOMES</t>
+  </si>
+  <si>
+    <t>FABIO BENEDITO CARRASCAL CRUZ</t>
+  </si>
+  <si>
+    <t>GABRIEL DE SOUZA ALVES</t>
+  </si>
+  <si>
+    <t>JULIANO ALBINO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JULIO CESAR AMARAL</t>
+  </si>
+  <si>
+    <t>PAULO HENRIQUE VENANCIO DE SOUZA</t>
   </si>
 </sst>
 </file>
@@ -7493,7 +7526,26 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -7803,7 +7855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2498"/>
+  <dimension ref="A1:C2509"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27804,8 +27856,99 @@
         <v>1447599</v>
       </c>
     </row>
+    <row r="2499" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2499" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B2499">
+        <v>1447711</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2500" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B2500">
+        <v>1447678</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2501" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B2501">
+        <v>1447657</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2502" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B2502">
+        <v>1447757</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2503" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B2503">
+        <v>1447730</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2504" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B2504">
+        <v>1447810</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2505" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B2505">
+        <v>1447822</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2506" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B2506">
+        <v>1447844</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2507" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B2507">
+        <v>1447816</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2508" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B2508">
+        <v>1447841</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2509" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B2509">
+        <v>1447812</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B2386" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
+  <autoFilter ref="A1:B2509" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8892D1A9-3A44-4AB0-B79E-38D674BA2D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28BE887-5ADF-417D-A292-0D716CC62E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="2472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="2473">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7455,6 +7455,9 @@
   </si>
   <si>
     <t>PAULO HENRIQUE VENANCIO DE SOUZA</t>
+  </si>
+  <si>
+    <t>MARCOS PAULO DA CONCEICAO LEOPOLDINO</t>
   </si>
 </sst>
 </file>
@@ -7526,15 +7529,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -7855,7 +7850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2509"/>
+  <dimension ref="A1:C2510"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27944,10 +27939,18 @@
         <v>1447812</v>
       </c>
     </row>
+    <row r="2510" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2510" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B2510">
+        <v>1447895</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2509" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28BE887-5ADF-417D-A292-0D716CC62E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FEA36D-557D-4720-9DA0-2122FD27C3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="2473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2519" uniqueCount="2480">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7458,6 +7458,27 @@
   </si>
   <si>
     <t>MARCOS PAULO DA CONCEICAO LEOPOLDINO</t>
+  </si>
+  <si>
+    <t>LUIZ MARCOS DE JESUS SANTOS</t>
+  </si>
+  <si>
+    <t>CARLOS GUSTAVO FERREIRA BARBOSA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>DANIEL MACEDO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JAILTON DOS SANTOS MIRANDA</t>
+  </si>
+  <si>
+    <t>LEONARDO FERREIRA INVENCAO</t>
+  </si>
+  <si>
+    <t>VINICIUS JESUS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JEFFERSON DE FREITAS SILVA</t>
   </si>
 </sst>
 </file>
@@ -7850,7 +7871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2510"/>
+  <dimension ref="A1:C2517"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27945,6 +27966,59 @@
       </c>
       <c r="B2510">
         <v>1447895</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2511" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B2511">
+        <v>1448088</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2512" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B2512">
+        <v>1448128</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2513" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B2513">
+        <v>1448122</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2514" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B2514">
+        <v>1448107</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2515" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2516" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B2516">
+        <v>1448063</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2517" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B2517">
+        <v>1448102</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FEA36D-557D-4720-9DA0-2122FD27C3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CB8E86-CA8D-4B9B-879E-6CC0D57BDC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CB8E86-CA8D-4B9B-879E-6CC0D57BDC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A24D0F8-5C96-4966-9189-3A140BBA7CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2519" uniqueCount="2480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="2480">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7871,7 +7871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2517"/>
+  <dimension ref="A1:F2517"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27856,7 +27856,7 @@
         <v>1447630</v>
       </c>
     </row>
-    <row r="2497" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2497" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2497" t="s">
         <v>2459</v>
       </c>
@@ -27864,7 +27864,7 @@
         <v>854218</v>
       </c>
     </row>
-    <row r="2498" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2498" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2498" t="s">
         <v>2460</v>
       </c>
@@ -27872,7 +27872,7 @@
         <v>1447599</v>
       </c>
     </row>
-    <row r="2499" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2499" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2499" t="s">
         <v>2461</v>
       </c>
@@ -27880,7 +27880,7 @@
         <v>1447711</v>
       </c>
     </row>
-    <row r="2500" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2500" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2500" t="s">
         <v>2462</v>
       </c>
@@ -27888,15 +27888,22 @@
         <v>1447678</v>
       </c>
     </row>
-    <row r="2501" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2501" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2501" t="s">
         <v>2463</v>
       </c>
       <c r="B2501">
         <v>1447657</v>
       </c>
-    </row>
-    <row r="2502" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E2501" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F2501" t="str">
+        <f>VLOOKUP(E2501,A:A,1,0)</f>
+        <v>HALBERT DOS SANTOS LEITE</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2502" t="s">
         <v>2464</v>
       </c>
@@ -27904,7 +27911,7 @@
         <v>1447757</v>
       </c>
     </row>
-    <row r="2503" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2503" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2503" t="s">
         <v>2465</v>
       </c>
@@ -27912,7 +27919,7 @@
         <v>1447730</v>
       </c>
     </row>
-    <row r="2504" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2504" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2504" t="s">
         <v>2466</v>
       </c>
@@ -27920,7 +27927,7 @@
         <v>1447810</v>
       </c>
     </row>
-    <row r="2505" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2505" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2505" t="s">
         <v>2467</v>
       </c>
@@ -27928,7 +27935,7 @@
         <v>1447822</v>
       </c>
     </row>
-    <row r="2506" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2506" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2506" t="s">
         <v>2468</v>
       </c>
@@ -27936,7 +27943,7 @@
         <v>1447844</v>
       </c>
     </row>
-    <row r="2507" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2507" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2507" t="s">
         <v>2469</v>
       </c>
@@ -27944,7 +27951,7 @@
         <v>1447816</v>
       </c>
     </row>
-    <row r="2508" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2508" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2508" t="s">
         <v>2470</v>
       </c>
@@ -27952,7 +27959,7 @@
         <v>1447841</v>
       </c>
     </row>
-    <row r="2509" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2509" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2509" t="s">
         <v>2471</v>
       </c>
@@ -27960,7 +27967,7 @@
         <v>1447812</v>
       </c>
     </row>
-    <row r="2510" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2510" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2510" t="s">
         <v>2472</v>
       </c>
@@ -27968,7 +27975,7 @@
         <v>1447895</v>
       </c>
     </row>
-    <row r="2511" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2511" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2511" t="s">
         <v>2473</v>
       </c>
@@ -27976,7 +27983,7 @@
         <v>1448088</v>
       </c>
     </row>
-    <row r="2512" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2512" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2512" t="s">
         <v>2474</v>
       </c>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9191A89E-8D4E-4D83-A9E3-FEE05711A97B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A76231-C49A-4464-AFD0-DAEE464C03E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IDs Logon'!$A$1:$B$2509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IDs Logon'!$A$1:$B$2508</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="2523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="2516">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7376,9 +7376,6 @@
     <t>JOSE RONALDSON SOUSA DA COSTA</t>
   </si>
   <si>
-    <t>ARTHUR NOGUEIRA DA CONCEICAO</t>
-  </si>
-  <si>
     <t>ALEXANDRE EDUARDO DA SILVA</t>
   </si>
   <si>
@@ -7481,15 +7478,6 @@
     <t>JEFFERSON DE FREITAS SILVA</t>
   </si>
   <si>
-    <t>ALISON MEDEIROS SILVA</t>
-  </si>
-  <si>
-    <t>MARCELO LIMA DOS SANTOS</t>
-  </si>
-  <si>
-    <t>OSENILSON SANTOS DE MACEDO</t>
-  </si>
-  <si>
     <t>ANDERSON JOSE DA SILVA</t>
   </si>
   <si>
@@ -7563,15 +7551,6 @@
   </si>
   <si>
     <t>1448561</t>
-  </si>
-  <si>
-    <t>737883</t>
-  </si>
-  <si>
-    <t>641680</t>
-  </si>
-  <si>
-    <t>1398671</t>
   </si>
   <si>
     <t>1448489</t>
@@ -8003,7 +7982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2542"/>
+  <dimension ref="A1:C2538"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -27890,7 +27869,7 @@
         <v>2445</v>
       </c>
       <c r="B2484" s="3">
-        <v>1410185</v>
+        <v>1447565</v>
       </c>
     </row>
     <row r="2485" spans="1:2" x14ac:dyDescent="0.3">
@@ -27898,7 +27877,7 @@
         <v>2446</v>
       </c>
       <c r="B2485" s="3">
-        <v>1447565</v>
+        <v>1447558</v>
       </c>
     </row>
     <row r="2486" spans="1:2" x14ac:dyDescent="0.3">
@@ -27906,23 +27885,23 @@
         <v>2447</v>
       </c>
       <c r="B2486" s="3">
-        <v>1447558</v>
+        <v>1447553</v>
       </c>
     </row>
     <row r="2487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2487" t="s">
         <v>2448</v>
       </c>
-      <c r="B2487" s="3">
-        <v>1447553</v>
+      <c r="B2487" s="3" t="s">
+        <v>2449</v>
       </c>
     </row>
     <row r="2488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2488" t="s">
-        <v>2449</v>
-      </c>
-      <c r="B2488" s="3" t="s">
         <v>2450</v>
+      </c>
+      <c r="B2488" s="3">
+        <v>1447608</v>
       </c>
     </row>
     <row r="2489" spans="1:2" x14ac:dyDescent="0.3">
@@ -27930,7 +27909,7 @@
         <v>2451</v>
       </c>
       <c r="B2489" s="3">
-        <v>1447608</v>
+        <v>1447617</v>
       </c>
     </row>
     <row r="2490" spans="1:2" x14ac:dyDescent="0.3">
@@ -27938,7 +27917,7 @@
         <v>2452</v>
       </c>
       <c r="B2490" s="3">
-        <v>1447617</v>
+        <v>1447598</v>
       </c>
     </row>
     <row r="2491" spans="1:2" x14ac:dyDescent="0.3">
@@ -27946,7 +27925,7 @@
         <v>2453</v>
       </c>
       <c r="B2491" s="3">
-        <v>1447598</v>
+        <v>1447609</v>
       </c>
     </row>
     <row r="2492" spans="1:2" x14ac:dyDescent="0.3">
@@ -27954,7 +27933,7 @@
         <v>2454</v>
       </c>
       <c r="B2492" s="3">
-        <v>1447609</v>
+        <v>1447596</v>
       </c>
     </row>
     <row r="2493" spans="1:2" x14ac:dyDescent="0.3">
@@ -27962,7 +27941,7 @@
         <v>2455</v>
       </c>
       <c r="B2493" s="3">
-        <v>1447596</v>
+        <v>1447606</v>
       </c>
     </row>
     <row r="2494" spans="1:2" x14ac:dyDescent="0.3">
@@ -27970,7 +27949,7 @@
         <v>2456</v>
       </c>
       <c r="B2494" s="3">
-        <v>1447606</v>
+        <v>1113248</v>
       </c>
     </row>
     <row r="2495" spans="1:2" x14ac:dyDescent="0.3">
@@ -27978,7 +27957,7 @@
         <v>2457</v>
       </c>
       <c r="B2495" s="3">
-        <v>1113248</v>
+        <v>1447630</v>
       </c>
     </row>
     <row r="2496" spans="1:2" x14ac:dyDescent="0.3">
@@ -27986,7 +27965,7 @@
         <v>2458</v>
       </c>
       <c r="B2496" s="3">
-        <v>1447630</v>
+        <v>854218</v>
       </c>
     </row>
     <row r="2497" spans="1:2" x14ac:dyDescent="0.3">
@@ -27994,7 +27973,7 @@
         <v>2459</v>
       </c>
       <c r="B2497" s="3">
-        <v>854218</v>
+        <v>1447599</v>
       </c>
     </row>
     <row r="2498" spans="1:2" x14ac:dyDescent="0.3">
@@ -28002,7 +27981,7 @@
         <v>2460</v>
       </c>
       <c r="B2498" s="3">
-        <v>1447599</v>
+        <v>1447711</v>
       </c>
     </row>
     <row r="2499" spans="1:2" x14ac:dyDescent="0.3">
@@ -28010,7 +27989,7 @@
         <v>2461</v>
       </c>
       <c r="B2499" s="3">
-        <v>1447711</v>
+        <v>1447678</v>
       </c>
     </row>
     <row r="2500" spans="1:2" x14ac:dyDescent="0.3">
@@ -28018,7 +27997,7 @@
         <v>2462</v>
       </c>
       <c r="B2500" s="3">
-        <v>1447678</v>
+        <v>1447657</v>
       </c>
     </row>
     <row r="2501" spans="1:2" x14ac:dyDescent="0.3">
@@ -28026,7 +28005,7 @@
         <v>2463</v>
       </c>
       <c r="B2501" s="3">
-        <v>1447657</v>
+        <v>1447757</v>
       </c>
     </row>
     <row r="2502" spans="1:2" x14ac:dyDescent="0.3">
@@ -28034,7 +28013,7 @@
         <v>2464</v>
       </c>
       <c r="B2502" s="3">
-        <v>1447757</v>
+        <v>1447730</v>
       </c>
     </row>
     <row r="2503" spans="1:2" x14ac:dyDescent="0.3">
@@ -28042,7 +28021,7 @@
         <v>2465</v>
       </c>
       <c r="B2503" s="3">
-        <v>1447730</v>
+        <v>1447810</v>
       </c>
     </row>
     <row r="2504" spans="1:2" x14ac:dyDescent="0.3">
@@ -28050,7 +28029,7 @@
         <v>2466</v>
       </c>
       <c r="B2504" s="3">
-        <v>1447810</v>
+        <v>1447822</v>
       </c>
     </row>
     <row r="2505" spans="1:2" x14ac:dyDescent="0.3">
@@ -28058,7 +28037,7 @@
         <v>2467</v>
       </c>
       <c r="B2505" s="3">
-        <v>1447822</v>
+        <v>1447844</v>
       </c>
     </row>
     <row r="2506" spans="1:2" x14ac:dyDescent="0.3">
@@ -28066,7 +28045,7 @@
         <v>2468</v>
       </c>
       <c r="B2506" s="3">
-        <v>1447844</v>
+        <v>1447816</v>
       </c>
     </row>
     <row r="2507" spans="1:2" x14ac:dyDescent="0.3">
@@ -28074,7 +28053,7 @@
         <v>2469</v>
       </c>
       <c r="B2507" s="3">
-        <v>1447816</v>
+        <v>1447841</v>
       </c>
     </row>
     <row r="2508" spans="1:2" x14ac:dyDescent="0.3">
@@ -28082,7 +28061,7 @@
         <v>2470</v>
       </c>
       <c r="B2508" s="3">
-        <v>1447841</v>
+        <v>1447812</v>
       </c>
     </row>
     <row r="2509" spans="1:2" x14ac:dyDescent="0.3">
@@ -28090,7 +28069,7 @@
         <v>2471</v>
       </c>
       <c r="B2509" s="3">
-        <v>1447812</v>
+        <v>1447895</v>
       </c>
     </row>
     <row r="2510" spans="1:2" x14ac:dyDescent="0.3">
@@ -28098,7 +28077,7 @@
         <v>2472</v>
       </c>
       <c r="B2510" s="3">
-        <v>1447895</v>
+        <v>1448088</v>
       </c>
     </row>
     <row r="2511" spans="1:2" x14ac:dyDescent="0.3">
@@ -28106,7 +28085,7 @@
         <v>2473</v>
       </c>
       <c r="B2511" s="3">
-        <v>1448088</v>
+        <v>1448128</v>
       </c>
     </row>
     <row r="2512" spans="1:2" x14ac:dyDescent="0.3">
@@ -28114,7 +28093,7 @@
         <v>2474</v>
       </c>
       <c r="B2512" s="3">
-        <v>1448128</v>
+        <v>1448122</v>
       </c>
     </row>
     <row r="2513" spans="1:2" x14ac:dyDescent="0.3">
@@ -28122,7 +28101,7 @@
         <v>2475</v>
       </c>
       <c r="B2513" s="3">
-        <v>1448122</v>
+        <v>1448107</v>
       </c>
     </row>
     <row r="2514" spans="1:2" x14ac:dyDescent="0.3">
@@ -28130,7 +28109,7 @@
         <v>2476</v>
       </c>
       <c r="B2514" s="3">
-        <v>1448107</v>
+        <v>1448408</v>
       </c>
     </row>
     <row r="2515" spans="1:2" x14ac:dyDescent="0.3">
@@ -28138,7 +28117,7 @@
         <v>2477</v>
       </c>
       <c r="B2515" s="3">
-        <v>1448408</v>
+        <v>1448063</v>
       </c>
     </row>
     <row r="2516" spans="1:2" x14ac:dyDescent="0.3">
@@ -28146,15 +28125,15 @@
         <v>2478</v>
       </c>
       <c r="B2516" s="3">
-        <v>1448063</v>
+        <v>1448102</v>
       </c>
     </row>
     <row r="2517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2517" t="s">
         <v>2479</v>
       </c>
-      <c r="B2517" s="3">
-        <v>1448102</v>
+      <c r="B2517" s="3" t="s">
+        <v>2504</v>
       </c>
     </row>
     <row r="2518" spans="1:2" x14ac:dyDescent="0.3">
@@ -28162,7 +28141,7 @@
         <v>2480</v>
       </c>
       <c r="B2518" s="3" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="2519" spans="1:2" x14ac:dyDescent="0.3">
@@ -28170,23 +28149,20 @@
         <v>2481</v>
       </c>
       <c r="B2519" s="3" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="2520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2520" t="s">
         <v>2482</v>
       </c>
-      <c r="B2520" s="3" t="s">
-        <v>2510</v>
-      </c>
     </row>
     <row r="2521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2521" t="s">
         <v>2483</v>
       </c>
       <c r="B2521" s="3" t="s">
-        <v>2511</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="2522" spans="1:2" x14ac:dyDescent="0.3">
@@ -28194,7 +28170,7 @@
         <v>2484</v>
       </c>
       <c r="B2522" s="3" t="s">
-        <v>2512</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="2523" spans="1:2" x14ac:dyDescent="0.3">
@@ -28202,20 +28178,23 @@
         <v>2485</v>
       </c>
       <c r="B2523" s="3" t="s">
-        <v>2513</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="2524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2524" t="s">
         <v>2486</v>
       </c>
+      <c r="B2524" s="3" t="s">
+        <v>2510</v>
+      </c>
     </row>
     <row r="2525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2525" t="s">
         <v>2487</v>
       </c>
       <c r="B2525" s="3" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="2526" spans="1:2" x14ac:dyDescent="0.3">
@@ -28223,7 +28202,7 @@
         <v>2488</v>
       </c>
       <c r="B2526" s="3" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="2527" spans="1:2" x14ac:dyDescent="0.3">
@@ -28231,7 +28210,7 @@
         <v>2489</v>
       </c>
       <c r="B2527" s="3" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="2528" spans="1:2" x14ac:dyDescent="0.3">
@@ -28239,7 +28218,7 @@
         <v>2490</v>
       </c>
       <c r="B2528" s="3" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="2529" spans="1:2" x14ac:dyDescent="0.3">
@@ -28247,7 +28226,7 @@
         <v>2491</v>
       </c>
       <c r="B2529" s="3" t="s">
-        <v>2518</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="2530" spans="1:2" x14ac:dyDescent="0.3">
@@ -28255,7 +28234,7 @@
         <v>2492</v>
       </c>
       <c r="B2530" s="3" t="s">
-        <v>2519</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="2531" spans="1:2" x14ac:dyDescent="0.3">
@@ -28263,47 +28242,47 @@
         <v>2493</v>
       </c>
       <c r="B2531" s="3" t="s">
-        <v>2520</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="2532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2532" t="s">
         <v>2494</v>
       </c>
-      <c r="B2532" s="3" t="s">
-        <v>2521</v>
+      <c r="B2532" s="3">
+        <v>1448673</v>
       </c>
     </row>
     <row r="2533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2533" t="s">
         <v>2495</v>
       </c>
-      <c r="B2533" s="3" t="s">
-        <v>2505</v>
+      <c r="B2533" s="3">
+        <v>1448662</v>
       </c>
     </row>
     <row r="2534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2534" t="s">
         <v>2496</v>
       </c>
-      <c r="B2534" s="3" t="s">
-        <v>2506</v>
+      <c r="B2534" s="3">
+        <v>1448641</v>
       </c>
     </row>
     <row r="2535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2535" t="s">
         <v>2497</v>
       </c>
-      <c r="B2535" s="3" t="s">
-        <v>2507</v>
+      <c r="B2535" s="3">
+        <v>1448639</v>
       </c>
     </row>
     <row r="2536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2536" t="s">
         <v>2498</v>
       </c>
-      <c r="B2536" s="3">
-        <v>1448673</v>
+      <c r="B2536" s="3" t="s">
+        <v>2515</v>
       </c>
     </row>
     <row r="2537" spans="1:2" x14ac:dyDescent="0.3">
@@ -28311,7 +28290,7 @@
         <v>2499</v>
       </c>
       <c r="B2537" s="3">
-        <v>1448662</v>
+        <v>1448649</v>
       </c>
     </row>
     <row r="2538" spans="1:2" x14ac:dyDescent="0.3">
@@ -28319,43 +28298,11 @@
         <v>2500</v>
       </c>
       <c r="B2538" s="3">
-        <v>1448641</v>
-      </c>
-    </row>
-    <row r="2539" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2539" t="s">
-        <v>2501</v>
-      </c>
-      <c r="B2539" s="3">
-        <v>1448639</v>
-      </c>
-    </row>
-    <row r="2540" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2540" t="s">
-        <v>2502</v>
-      </c>
-      <c r="B2540" s="3" t="s">
-        <v>2522</v>
-      </c>
-    </row>
-    <row r="2541" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2541" t="s">
-        <v>2503</v>
-      </c>
-      <c r="B2541" s="3">
-        <v>1448649</v>
-      </c>
-    </row>
-    <row r="2542" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2542" t="s">
-        <v>2504</v>
-      </c>
-      <c r="B2542" s="3">
         <v>1448645</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B2509" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
+  <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A76231-C49A-4464-AFD0-DAEE464C03E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EF071B-3F02-46D2-B2F5-A149BD31E3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>
@@ -7987,6 +7987,7 @@
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -28155,6 +28156,9 @@
     <row r="2520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2520" t="s">
         <v>2482</v>
+      </c>
+      <c r="B2520" s="3">
+        <v>1448430</v>
       </c>
     </row>
     <row r="2521" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EF071B-3F02-46D2-B2F5-A149BD31E3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD05B895-8AFE-4ABF-BBE8-279B5DC60BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD05B895-8AFE-4ABF-BBE8-279B5DC60BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E46E2C-E7FC-4506-A4B1-D4E26CA3AE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E46E2C-E7FC-4506-A4B1-D4E26CA3AE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E664EC-AFEE-4235-8F13-120E294A74B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="2516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2553" uniqueCount="2514">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7535,9 +7535,6 @@
     <t>ROGERIO CARLOS DA SILVA</t>
   </si>
   <si>
-    <t>UANDERSON CARVALHO DE SANTANA</t>
-  </si>
-  <si>
     <t>DIEGO DA SILVA TELES</t>
   </si>
   <si>
@@ -7584,9 +7581,6 @@
   </si>
   <si>
     <t>1448356</t>
-  </si>
-  <si>
-    <t>1394712</t>
   </si>
 </sst>
 </file>
@@ -7982,7 +7976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2538"/>
+  <dimension ref="A1:C2537"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28134,7 +28128,7 @@
         <v>2479</v>
       </c>
       <c r="B2517" s="3" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="2518" spans="1:2" x14ac:dyDescent="0.3">
@@ -28142,7 +28136,7 @@
         <v>2480</v>
       </c>
       <c r="B2518" s="3" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="2519" spans="1:2" x14ac:dyDescent="0.3">
@@ -28150,7 +28144,7 @@
         <v>2481</v>
       </c>
       <c r="B2519" s="3" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="2520" spans="1:2" x14ac:dyDescent="0.3">
@@ -28166,7 +28160,7 @@
         <v>2483</v>
       </c>
       <c r="B2521" s="3" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="2522" spans="1:2" x14ac:dyDescent="0.3">
@@ -28174,7 +28168,7 @@
         <v>2484</v>
       </c>
       <c r="B2522" s="3" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="2523" spans="1:2" x14ac:dyDescent="0.3">
@@ -28182,7 +28176,7 @@
         <v>2485</v>
       </c>
       <c r="B2523" s="3" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="2524" spans="1:2" x14ac:dyDescent="0.3">
@@ -28190,7 +28184,7 @@
         <v>2486</v>
       </c>
       <c r="B2524" s="3" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="2525" spans="1:2" x14ac:dyDescent="0.3">
@@ -28198,7 +28192,7 @@
         <v>2487</v>
       </c>
       <c r="B2525" s="3" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="2526" spans="1:2" x14ac:dyDescent="0.3">
@@ -28206,7 +28200,7 @@
         <v>2488</v>
       </c>
       <c r="B2526" s="3" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="2527" spans="1:2" x14ac:dyDescent="0.3">
@@ -28214,7 +28208,7 @@
         <v>2489</v>
       </c>
       <c r="B2527" s="3" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="2528" spans="1:2" x14ac:dyDescent="0.3">
@@ -28222,7 +28216,7 @@
         <v>2490</v>
       </c>
       <c r="B2528" s="3" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="2529" spans="1:2" x14ac:dyDescent="0.3">
@@ -28230,7 +28224,7 @@
         <v>2491</v>
       </c>
       <c r="B2529" s="3" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="2530" spans="1:2" x14ac:dyDescent="0.3">
@@ -28238,7 +28232,7 @@
         <v>2492</v>
       </c>
       <c r="B2530" s="3" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="2531" spans="1:2" x14ac:dyDescent="0.3">
@@ -28246,7 +28240,7 @@
         <v>2493</v>
       </c>
       <c r="B2531" s="3" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="2532" spans="1:2" x14ac:dyDescent="0.3">
@@ -28285,8 +28279,8 @@
       <c r="A2536" t="s">
         <v>2498</v>
       </c>
-      <c r="B2536" s="3" t="s">
-        <v>2515</v>
+      <c r="B2536" s="3">
+        <v>1448649</v>
       </c>
     </row>
     <row r="2537" spans="1:2" x14ac:dyDescent="0.3">
@@ -28294,14 +28288,6 @@
         <v>2499</v>
       </c>
       <c r="B2537" s="3">
-        <v>1448649</v>
-      </c>
-    </row>
-    <row r="2538" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2538" t="s">
-        <v>2500</v>
-      </c>
-      <c r="B2538" s="3">
         <v>1448645</v>
       </c>
     </row>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E494FE-395C-464E-8B0D-8E59ECE384E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A3B2CD-D9FB-4372-8838-9530F254523D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A3B2CD-D9FB-4372-8838-9530F254523D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E01F37B-C8A8-47BC-BC02-C8EA1710F9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="2516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2557" uniqueCount="2518">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7587,6 +7587,12 @@
   </si>
   <si>
     <t>MARCOS ANTONIO SOUZA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>ISAQUE SOARES MURICI</t>
+  </si>
+  <si>
+    <t>JORGE COSTA FEITOZA</t>
   </si>
 </sst>
 </file>
@@ -7982,7 +7988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2539"/>
+  <dimension ref="A1:C2541"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
@@ -28313,6 +28319,22 @@
         <v>1400600</v>
       </c>
     </row>
+    <row r="2540" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2540" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B2540" s="3">
+        <v>1449101</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2541" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B2541" s="3">
+        <v>1449085</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F410B664-CD5F-41C3-B29D-9CB37CA53AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB74C5F-D895-4337-A57C-46790BC1816F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -8003,7 +8003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:G2582"/>
+  <dimension ref="A1:C2546"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28390,114 +28390,6 @@
         <v>1449248</v>
       </c>
     </row>
-    <row r="2565" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2565" t="e">
-        <f t="shared" ref="G2535:G2582" si="0">VLOOKUP(F2565,A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2566" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2566" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2567" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2567" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2568" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2568" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2569" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2569" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2570" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2570" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2571" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2571" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2572" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2572" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2573" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2573" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2574" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2574" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2575" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2575" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2576" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2576" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2577" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2577" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2578" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2578" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2579" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2579" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2580" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2580" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2581" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2581" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="2582" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G2582" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A36D050-ACEC-4652-9A51-F0DAC2CF8C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133E3A71-68D3-47B1-8C6F-C3CBA6AADFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="2526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2567" uniqueCount="2528">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7617,13 +7617,19 @@
   </si>
   <si>
     <t>LUCIANO FELIX DE FIGUEREDO</t>
+  </si>
+  <si>
+    <t>JONATHA HENRIQUE CARNEIRO CUNHA</t>
+  </si>
+  <si>
+    <t>MAYCKON JUNIOR DE OLIVEIRA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7636,6 +7642,11 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="3">
@@ -7678,7 +7689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7686,6 +7697,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8012,7 +8026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2549"/>
+  <dimension ref="A1:C2551"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" bestFit="1" customWidth="1"/>
@@ -28423,6 +28437,22 @@
         <v>1449390</v>
       </c>
     </row>
+    <row r="2550" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2550" s="4" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B2550" s="3">
+        <v>1449634</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2551" s="4" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B2551" s="3">
+        <v>1449625</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AFC474-E413-49EB-979C-DD86D306561F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EC7A14-7D1F-4CCC-A427-411FA333B2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="2529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2578" uniqueCount="2539">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7626,6 +7626,36 @@
   </si>
   <si>
     <t>DIOGO DIAS CARDOSO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>ADELSON GOMES DA SILVA</t>
+  </si>
+  <si>
+    <t>ALEF DANIEL DA SILVA</t>
+  </si>
+  <si>
+    <t>FABIO RODRIGUES MONCAO</t>
+  </si>
+  <si>
+    <t>GABRIEL MOURA ALVES</t>
+  </si>
+  <si>
+    <t>IVAN DE OLIVEIRA MARTINS</t>
+  </si>
+  <si>
+    <t>LUCAS DE PONTES BATISTA</t>
+  </si>
+  <si>
+    <t>RAIMUNDO DACIEL SANTOS DA SILVA</t>
+  </si>
+  <si>
+    <t>JEFFERSON ALVES SAMPAIO</t>
+  </si>
+  <si>
+    <t>VAGNER EVANGELISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	1449728</t>
   </si>
 </sst>
 </file>
@@ -8029,7 +8059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2552"/>
+  <dimension ref="A1:C2561"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28464,6 +28494,78 @@
         <v>1449702</v>
       </c>
     </row>
+    <row r="2553" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2553" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B2553" s="3">
+        <v>1449731</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2554" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B2554" s="3" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2555" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B2555" s="3">
+        <v>1449729</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2556" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B2556" s="3">
+        <v>1149939</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2557" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B2557" s="3">
+        <v>1449727</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2558" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2558" s="3">
+        <v>1449723</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2559" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B2559" s="3">
+        <v>1449722</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2560" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B2560" s="3">
+        <v>1449741</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2561" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2561" s="3">
+        <v>1449737</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EC7A14-7D1F-4CCC-A427-411FA333B2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FA8ED0-C2F1-4A3F-9794-9800C94D6051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2578" uniqueCount="2539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="2540">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7656,6 +7656,9 @@
   </si>
   <si>
     <t xml:space="preserve">	1449728</t>
+  </si>
+  <si>
+    <t>DANILO SANTOS SILVA</t>
   </si>
 </sst>
 </file>
@@ -8059,7 +8062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2561"/>
+  <dimension ref="A1:C2562"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28566,6 +28569,11 @@
         <v>1449737</v>
       </c>
     </row>
+    <row r="2562" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2562" s="4" t="s">
+        <v>2539</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FA8ED0-C2F1-4A3F-9794-9800C94D6051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50479AD3-F586-443C-98EC-13EEED469590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="2540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="2544">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7659,6 +7659,18 @@
   </si>
   <si>
     <t>DANILO SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>ANDRE LUIZ TEIXEIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>GILDEON MUNIZ PEREIRA</t>
+  </si>
+  <si>
+    <t>JEFFERSON RIBEIRO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JOSSIVALDO NASCIMENTO DA LUZ</t>
   </si>
 </sst>
 </file>
@@ -8062,7 +8074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2562"/>
+  <dimension ref="A1:C2566"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28573,6 +28585,41 @@
       <c r="A2562" s="4" t="s">
         <v>2539</v>
       </c>
+      <c r="B2562" s="3">
+        <v>1449758</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2563" s="4" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B2563" s="3">
+        <v>1449927</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2564" s="4" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B2564" s="3">
+        <v>1449921</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2565" s="4" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B2565" s="3">
+        <v>1449918</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2566" s="4" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B2566" s="3">
+        <v>1449911</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50479AD3-F586-443C-98EC-13EEED469590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B1131E-9C43-48D5-B962-D433F6B1DDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="2544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="2549">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7671,6 +7671,21 @@
   </si>
   <si>
     <t>JOSSIVALDO NASCIMENTO DA LUZ</t>
+  </si>
+  <si>
+    <t>LUIS MELQUIDES DE SOUZA</t>
+  </si>
+  <si>
+    <t>PEDRO AUGUSTO DOS SANTOS TOMAZ</t>
+  </si>
+  <si>
+    <t>PEDRO HENRIQUE MOREIRA</t>
+  </si>
+  <si>
+    <t>TIAGO DA COSTA MACHADO</t>
+  </si>
+  <si>
+    <t>VINICIUS ALEXANDRE DANKO</t>
   </si>
 </sst>
 </file>
@@ -7695,6 +7710,7 @@
       <sz val="9.75"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -8074,7 +8090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2566"/>
+  <dimension ref="A1:C2571"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28621,6 +28637,34 @@
         <v>1449911</v>
       </c>
     </row>
+    <row r="2567" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2567" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B2567" s="3">
+        <v>1449970</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2568" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2569" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2570" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2571" t="s">
+        <v>2548</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B1131E-9C43-48D5-B962-D433F6B1DDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8524D85B-8AF7-48F4-A3B7-527E1ADA3738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -28649,20 +28649,32 @@
       <c r="A2568" t="s">
         <v>2545</v>
       </c>
+      <c r="B2568" s="3">
+        <v>1450037</v>
+      </c>
     </row>
     <row r="2569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2569" t="s">
         <v>2546</v>
       </c>
+      <c r="B2569" s="3">
+        <v>1450036</v>
+      </c>
     </row>
     <row r="2570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2570" t="s">
         <v>2547</v>
       </c>
+      <c r="B2570" s="3">
+        <v>1450025</v>
+      </c>
     </row>
     <row r="2571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2571" t="s">
         <v>2548</v>
+      </c>
+      <c r="B2571" s="3">
+        <v>1450024</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8524D85B-8AF7-48F4-A3B7-527E1ADA3738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ADE5FB-2991-4C7D-8D39-1E64B037220B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="2549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="2557">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7686,6 +7686,30 @@
   </si>
   <si>
     <t>VINICIUS ALEXANDRE DANKO</t>
+  </si>
+  <si>
+    <t>DIEGO TADEU REIS</t>
+  </si>
+  <si>
+    <t>DIOGO DONIZETE FERREIRA LIMA</t>
+  </si>
+  <si>
+    <t>JOSEMAR OLIVEIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t>JOSUE ALVES DA COSTA</t>
+  </si>
+  <si>
+    <t>LUCAS CRUZ SIQUEIRA</t>
+  </si>
+  <si>
+    <t>VITOR EDUARDO NICULAU DOS SANTOS</t>
+  </si>
+  <si>
+    <t>LUAN LENON DA SILVA SANTOS</t>
+  </si>
+  <si>
+    <t>WILLIAM FELIPE LIMA DE PAULA</t>
   </si>
 </sst>
 </file>
@@ -8090,7 +8114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2571"/>
+  <dimension ref="A1:C2579"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28677,6 +28701,70 @@
         <v>1450024</v>
       </c>
     </row>
+    <row r="2572" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2572" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B2572" s="3">
+        <v>1450175</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2573" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B2573" s="3">
+        <v>1450173</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2574" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B2574" s="3">
+        <v>1450197</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2575" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B2575" s="3">
+        <v>1450199</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2576" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B2576" s="3">
+        <v>1450195</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2577" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B2577" s="3">
+        <v>1450184</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2578" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B2578" s="3">
+        <v>1450242</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2579" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B2579" s="3">
+        <v>1450231</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ADE5FB-2991-4C7D-8D39-1E64B037220B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C90D3A-98F7-4BF1-A34F-7F253D4EE16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="2557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2597" uniqueCount="2558">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7710,6 +7710,9 @@
   </si>
   <si>
     <t>WILLIAM FELIPE LIMA DE PAULA</t>
+  </si>
+  <si>
+    <t>EMERSON SANTOS COSTA</t>
   </si>
 </sst>
 </file>
@@ -8114,7 +8117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2579"/>
+  <dimension ref="A1:C2580"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28765,6 +28768,14 @@
         <v>1450231</v>
       </c>
     </row>
+    <row r="2580" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2580" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B2580" s="3">
+        <v>1450369</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C90D3A-98F7-4BF1-A34F-7F253D4EE16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3AD0BF-4DBA-4727-BAED-EF318E8B675C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\novo_portal_rh\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3AD0BF-4DBA-4727-BAED-EF318E8B675C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714BEC3E-7FCF-4263-9BBA-B168C093B496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2597" uniqueCount="2558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2600" uniqueCount="2561">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7713,25 +7713,28 @@
   </si>
   <si>
     <t>EMERSON SANTOS COSTA</t>
+  </si>
+  <si>
+    <t>ELIONALDO VICENTE MARQUES DA SILVA</t>
+  </si>
+  <si>
+    <t>FELIPE CARDOSO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>IGOR MENDES SAO JOSE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="9.75"/>
@@ -7780,7 +7783,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7788,9 +7791,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8117,7 +8117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2580"/>
+  <dimension ref="A1:C2583"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28529,7 +28529,7 @@
       </c>
     </row>
     <row r="2550" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2550" s="4" t="s">
+      <c r="A2550" s="2" t="s">
         <v>2526</v>
       </c>
       <c r="B2550" s="3">
@@ -28537,7 +28537,7 @@
       </c>
     </row>
     <row r="2551" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2551" s="4" t="s">
+      <c r="A2551" s="2" t="s">
         <v>2527</v>
       </c>
       <c r="B2551" s="3">
@@ -28545,7 +28545,7 @@
       </c>
     </row>
     <row r="2552" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2552" s="4" t="s">
+      <c r="A2552" s="2" t="s">
         <v>2528</v>
       </c>
       <c r="B2552" s="3">
@@ -28625,7 +28625,7 @@
       </c>
     </row>
     <row r="2562" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2562" s="4" t="s">
+      <c r="A2562" s="2" t="s">
         <v>2539</v>
       </c>
       <c r="B2562" s="3">
@@ -28633,7 +28633,7 @@
       </c>
     </row>
     <row r="2563" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2563" s="4" t="s">
+      <c r="A2563" s="2" t="s">
         <v>2540</v>
       </c>
       <c r="B2563" s="3">
@@ -28641,7 +28641,7 @@
       </c>
     </row>
     <row r="2564" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2564" s="4" t="s">
+      <c r="A2564" s="2" t="s">
         <v>2541</v>
       </c>
       <c r="B2564" s="3">
@@ -28649,7 +28649,7 @@
       </c>
     </row>
     <row r="2565" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2565" s="4" t="s">
+      <c r="A2565" s="2" t="s">
         <v>2542</v>
       </c>
       <c r="B2565" s="3">
@@ -28657,7 +28657,7 @@
       </c>
     </row>
     <row r="2566" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2566" s="4" t="s">
+      <c r="A2566" s="2" t="s">
         <v>2543</v>
       </c>
       <c r="B2566" s="3">
@@ -28774,6 +28774,30 @@
       </c>
       <c r="B2580" s="3">
         <v>1450369</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2581" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B2581" s="3">
+        <v>1450593</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2582" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B2582" s="3">
+        <v>1450580</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2583" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B2583" s="3">
+        <v>1450572</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\novo_portal_rh\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714BEC3E-7FCF-4263-9BBA-B168C093B496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545CB1DB-6D71-40E0-B599-15AE94330AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2600" uniqueCount="2561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2602" uniqueCount="2563">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7722,6 +7722,12 @@
   </si>
   <si>
     <t>IGOR MENDES SAO JOSE</t>
+  </si>
+  <si>
+    <t>ARTHUR VINICIUS MORAES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JHONN KAUAN MENEZES DO NASCIMENTO</t>
   </si>
 </sst>
 </file>
@@ -8117,7 +8123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2583"/>
+  <dimension ref="A1:C2585"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28800,6 +28806,22 @@
         <v>1450572</v>
       </c>
     </row>
+    <row r="2584" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2584" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B2584" s="3">
+        <v>1450735</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2585" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B2585" s="3">
+        <v>1450724</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\novo_portal_rh\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545CB1DB-6D71-40E0-B599-15AE94330AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E72747-4E07-46DB-9F8A-13CFFC8AC91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
   <sheets>
     <sheet name="IDs Logon" sheetId="1" r:id="rId1"/>

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\novo_portal_rh\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E72747-4E07-46DB-9F8A-13CFFC8AC91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B045F6E4-53FD-498D-A41F-F372F1EC1596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2602" uniqueCount="2563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="2569">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7728,6 +7728,24 @@
   </si>
   <si>
     <t>JHONN KAUAN MENEZES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>EMANUEL COSTA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JOSEILDO JOSE SANTANA DA SILVA</t>
+  </si>
+  <si>
+    <t>LOURIVALDO DOS SANTOS NEVES</t>
+  </si>
+  <si>
+    <t>PEDRO SILVA BITENCOURT</t>
+  </si>
+  <si>
+    <t>CLAUDEMIR CHRISTOVAO</t>
+  </si>
+  <si>
+    <t>VINICIUS VIEIRA DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -8123,7 +8141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2585"/>
+  <dimension ref="A1:C2591"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28822,6 +28840,54 @@
         <v>1450724</v>
       </c>
     </row>
+    <row r="2586" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2586" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2586" s="3">
+        <v>1450856</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2587" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B2587" s="3">
+        <v>450844</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2588" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B2588" s="3">
+        <v>1450852</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2589" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B2589" s="3">
+        <v>1426629</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2590" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B2590" s="3">
+        <v>1450858</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2591" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B2591" s="3">
+        <v>1450847</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\novo_portal_rh\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B045F6E4-53FD-498D-A41F-F372F1EC1596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E3CA85-B394-4936-ADC8-846B32315230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="2569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="2574">
   <si>
     <t>HENRRY LORENZO MORALES</t>
   </si>
@@ -7746,6 +7746,21 @@
   </si>
   <si>
     <t>VINICIUS VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>ELOIR DIEGO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>JHONI DE FREITAS EVANGELISTA</t>
+  </si>
+  <si>
+    <t>MIGUEL ARCHANJO DE ASSUMPCAO</t>
+  </si>
+  <si>
+    <t>RAFAEL PEREIRA SILVEIRA</t>
+  </si>
+  <si>
+    <t>RENATO DOS SANTOS FERREIRA</t>
   </si>
 </sst>
 </file>
@@ -8141,7 +8156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}">
-  <dimension ref="A1:C2591"/>
+  <dimension ref="A1:C2596"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -28888,6 +28903,46 @@
         <v>1450847</v>
       </c>
     </row>
+    <row r="2592" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2592" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B2592" s="3">
+        <v>1450930</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2593" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B2593" s="3">
+        <v>1450928</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2594" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B2594" s="3">
+        <v>1450923</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2595" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B2595" s="3">
+        <v>1450925</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2596" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B2596" s="3">
+        <v>1450926</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B2508" xr:uid="{37811A77-B5C5-4D9E-A4A2-96AAFB083F23}"/>
   <conditionalFormatting sqref="B1:B1048576">

--- a/data/Base IDs Logon.xlsx
+++ b/data/Base IDs Logon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\novo_portal_rh\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E3CA85-B394-4936-ADC8-846B32315230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7567AC-D512-4E1B-8670-16FE253AF6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89966862-49E0-41D0-ADE9-AE18940B15F8}"/>
   </bookViews>
